--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
